--- a/output/pdf_financials_xlsx/CPI.xlsx
+++ b/output/pdf_financials_xlsx/CPI.xlsx
@@ -978,19 +978,19 @@
         <v>0.061015</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.20689</v>
+        <v>1.701332</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.104822</v>
+        <v>0.747609</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.094434</v>
+        <v>0.419603</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.08884599999999999</v>
+        <v>0.365278</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.130504</v>
+        <v>0.9918169999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1041,19 +1041,19 @@
         <v>-0.061015</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.20689</v>
+        <v>-1.701332</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.104822</v>
+        <v>-0.747609</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.094434</v>
+        <v>-0.419603</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.08884599999999999</v>
+        <v>-0.365278</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.130504</v>
+        <v>-0.9918169999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.011617</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000121</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-9.31743</v>
+        <v>-9.329046999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.171961</v>
+        <v>-1.172082</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.471714</v>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-9.31743</v>
+        <v>-9.329046999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.171961</v>
+        <v>-1.172082</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.471714</v>
@@ -2507,31 +2507,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.018785</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001733</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.083053</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.019665</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.018505</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000993</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002317</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.08915099999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.247583</v>
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
@@ -2539,22 +2539,22 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.275232</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.055833</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.406993</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.236273</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.227209</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.931567</v>
       </c>
     </row>
     <row r="35">
@@ -2621,31 +2621,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.058845</v>
+        <v>0.07763</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001733</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.083053</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.019665</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.018505</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000993</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.002317</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.08915099999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.247583</v>
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
@@ -2653,22 +2653,22 @@
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.275232</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.055833</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>7.5</v>
+        <v>8.906993</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>4.675</v>
+        <v>4.911273</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>3.025</v>
+        <v>3.252209</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>2.75</v>
+        <v>3.681567</v>
       </c>
     </row>
     <row r="37">
@@ -3305,31 +3305,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.025873</v>
+        <v>0.007088</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.008614</v>
+        <v>0.006881</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.8331769999999999</v>
+        <v>0.750124</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.006679</v>
+        <v>0.9870139999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.032093</v>
+        <v>1.013588</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.006543</v>
+        <v>0.00555</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.004783</v>
+        <v>0.002466</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.09117</v>
+        <v>0.002019</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.251523</v>
+        <v>0.00394</v>
       </c>
       <c r="K48" s="1" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.585401</v>
+        <v>0.310169</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.011907</v>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -9016,7 +9016,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -18420,7 +18424,11 @@
           <t>Write-off of reclamation deposits</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -21232,7 +21240,11 @@
           <t>Additions to reclamation deposits</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -31464,7 +31476,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -31523,19 +31535,19 @@
         </is>
       </c>
       <c r="P247" s="5" t="n">
-        <v>-1.701332</v>
+        <v>1.701332</v>
       </c>
       <c r="Q247" s="5" t="n">
-        <v>-0.747609</v>
+        <v>0.747609</v>
       </c>
       <c r="R247" s="5" t="n">
-        <v>-0.419603</v>
+        <v>0.419603</v>
       </c>
       <c r="S247" s="5" t="n">
-        <v>-0.365278</v>
+        <v>0.365278</v>
       </c>
       <c r="T247" s="5" t="n">
-        <v>-0.9918169999999999</v>
+        <v>0.9918169999999999</v>
       </c>
     </row>
     <row r="248">
@@ -38732,7 +38744,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E324" s="5" t="n">
